--- a/outputs/monitor_xlsx/20260210.xlsx
+++ b/outputs/monitor_xlsx/20260210.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1107,40 +1110,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1193,12 +1191,7 @@
       <c r="N4" t="n">
         <v>3.79</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1236,12 +1229,7 @@
       <c r="M5" t="n">
         <v>-29281</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1294,12 +1282,7 @@
       <c r="N6" t="n">
         <v>1.73</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1352,12 +1335,7 @@
       <c r="N7" t="n">
         <v>-4.43</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1410,12 +1388,7 @@
       <c r="N8" t="n">
         <v>0.17</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1468,12 +1441,7 @@
       <c r="N9" t="n">
         <v>5.09</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1526,12 +1494,7 @@
       <c r="N10" t="n">
         <v>-0.82</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1584,12 +1547,7 @@
       <c r="N11" t="n">
         <v>6.85</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1642,12 +1600,7 @@
       <c r="N12" t="n">
         <v>0.92</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1700,12 +1653,7 @@
       <c r="N13" t="n">
         <v>-3.64</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1755,12 +1703,7 @@
       <c r="N14" t="n">
         <v>10.4</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1810,12 +1753,7 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1865,12 +1803,7 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1917,12 +1850,7 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1972,12 +1900,7 @@
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2030,12 +1953,7 @@
       <c r="N19" t="n">
         <v>-0.78</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2085,11 +2003,6 @@
       <c r="N20" t="n">
         <v>-0.97</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2138,11 +2051,6 @@
       <c r="N21" t="n">
         <v>-6.12</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2191,11 +2099,6 @@
       <c r="N22" t="n">
         <v>-7.64</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2244,11 +2147,6 @@
       <c r="N23" t="n">
         <v>16.86</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2297,11 +2195,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2350,11 +2243,6 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2403,11 +2291,6 @@
       <c r="N26" t="n">
         <v>3.15</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2455,11 +2338,6 @@
       </c>
       <c r="N27" t="n">
         <v>5.87</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260210.xlsx
+++ b/outputs/monitor_xlsx/20260210.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1152,44 +1149,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>75.5</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>2.1</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="7" t="n">
         <v>102315</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>23352</v>
       </c>
-      <c r="G4" t="n">
-        <v>-55232</v>
-      </c>
       <c r="H4" t="n">
+        <v>-31467</v>
+      </c>
+      <c r="I4" t="n">
         <v>4526</v>
       </c>
-      <c r="I4" t="n">
-        <v>6400</v>
-      </c>
       <c r="J4" t="n">
+        <v>10926</v>
+      </c>
+      <c r="K4" t="n">
         <v>16581</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7207</v>
       </c>
-      <c r="L4" t="n">
-        <v>38221</v>
-      </c>
       <c r="M4" t="n">
+        <v>37778</v>
+      </c>
+      <c r="N4" t="n">
         <v>-4036341</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.79</v>
+      <c r="O4" t="n">
+        <v>4.06</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1246,41 +1248,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>966</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>2.22</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="6" t="n">
         <v>3904</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>-1</v>
       </c>
-      <c r="G6" t="n">
-        <v>-882</v>
-      </c>
       <c r="H6" t="n">
+        <v>37</v>
+      </c>
+      <c r="I6" t="n">
         <v>18</v>
       </c>
-      <c r="I6" t="n">
-        <v>-29</v>
-      </c>
       <c r="J6" t="n">
+        <v>120</v>
+      </c>
+      <c r="K6" t="n">
         <v>67</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2875</v>
       </c>
-      <c r="L6" t="n">
-        <v>14259</v>
-      </c>
       <c r="M6" t="n">
+        <v>14359</v>
+      </c>
+      <c r="N6" t="n">
         <v>-78748</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.73</v>
+      <c r="O6" t="n">
+        <v>-1.35</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1352,41 +1359,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1185</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>0.42</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="6" t="n">
         <v>8355</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>-929</v>
       </c>
-      <c r="G8" t="n">
-        <v>-7045</v>
-      </c>
       <c r="H8" t="n">
+        <v>-6864</v>
+      </c>
+      <c r="I8" t="n">
         <v>9</v>
       </c>
-      <c r="I8" t="n">
-        <v>515</v>
-      </c>
       <c r="J8" t="n">
+        <v>564</v>
+      </c>
+      <c r="K8" t="n">
         <v>194</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6254</v>
       </c>
-      <c r="L8" t="n">
-        <v>30551</v>
-      </c>
       <c r="M8" t="n">
+        <v>30522</v>
+      </c>
+      <c r="N8" t="n">
         <v>-648673</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.17</v>
+      <c r="O8" t="n">
+        <v>0.3</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1405,41 +1417,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1880</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>3.58</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="7" t="n">
         <v>45674</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="7" t="n">
         <v>12634</v>
       </c>
-      <c r="G9" t="n">
-        <v>-25892</v>
-      </c>
       <c r="H9" t="n">
+        <v>-10335</v>
+      </c>
+      <c r="I9" t="n">
         <v>241</v>
       </c>
-      <c r="I9" t="n">
-        <v>4388</v>
-      </c>
       <c r="J9" t="n">
+        <v>3546</v>
+      </c>
+      <c r="K9" t="n">
         <v>1148</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>21244</v>
       </c>
-      <c r="L9" t="n">
-        <v>113171</v>
-      </c>
       <c r="M9" t="n">
+        <v>112536</v>
+      </c>
+      <c r="N9" t="n">
         <v>-6482883</v>
       </c>
-      <c r="N9" t="n">
-        <v>5.09</v>
+      <c r="O9" t="n">
+        <v>6.01</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1511,41 +1528,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>2105</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="7" t="n">
         <v>3163</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="G11" t="n">
-        <v>-320</v>
-      </c>
       <c r="H11" t="n">
+        <v>-369</v>
+      </c>
+      <c r="I11" t="n">
         <v>79</v>
       </c>
-      <c r="I11" t="n">
-        <v>1376</v>
-      </c>
       <c r="J11" t="n">
+        <v>1349</v>
+      </c>
+      <c r="K11" t="n">
         <v>68</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>2070</v>
       </c>
-      <c r="L11" t="n">
-        <v>10738</v>
-      </c>
       <c r="M11" t="n">
+        <v>10715</v>
+      </c>
+      <c r="N11" t="n">
         <v>-89474</v>
       </c>
-      <c r="N11" t="n">
-        <v>6.85</v>
+      <c r="O11" t="n">
+        <v>17.55</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1670,38 +1692,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>1985</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>7.3</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="7" t="n">
         <v>1317</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>245</v>
       </c>
-      <c r="G14" t="n">
-        <v>-122</v>
+      <c r="H14" t="n">
+        <v>398</v>
       </c>
       <c r="I14" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K14" t="n">
         <v>11</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4240</v>
       </c>
-      <c r="L14" t="n">
-        <v>21898</v>
-      </c>
       <c r="M14" t="n">
+        <v>21693</v>
+      </c>
+      <c r="N14" t="n">
         <v>-19223</v>
       </c>
-      <c r="N14" t="n">
-        <v>10.4</v>
+      <c r="O14" t="n">
+        <v>28.75</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1720,37 +1750,45 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1120</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="E15" t="n">
-        <v>583</v>
+        <v>2365</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.16</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="G15" t="n">
-        <v>919</v>
-      </c>
       <c r="H15" t="n">
+        <v>516</v>
+      </c>
+      <c r="I15" t="n">
         <v>52</v>
       </c>
-      <c r="I15" t="n">
-        <v>-82</v>
-      </c>
       <c r="J15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K15" t="n">
         <v>-8</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-47</v>
       </c>
-      <c r="L15" t="n">
-        <v>-492</v>
-      </c>
       <c r="M15" t="n">
+        <v>-416</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="inlineStr">
@@ -1867,37 +1905,45 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>333.5</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="E18" t="n">
-        <v>45207</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>586</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>9.94</v>
       </c>
       <c r="F18" s="6" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="6" t="n">
         <v>-2340</v>
       </c>
-      <c r="G18" t="n">
-        <v>2349</v>
-      </c>
       <c r="H18" t="n">
+        <v>1869</v>
+      </c>
+      <c r="I18" t="n">
         <v>467</v>
       </c>
-      <c r="I18" t="n">
-        <v>2985</v>
-      </c>
       <c r="J18" t="n">
+        <v>3198</v>
+      </c>
+      <c r="K18" t="n">
         <v>-226</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-619</v>
       </c>
-      <c r="L18" t="n">
-        <v>51</v>
-      </c>
       <c r="M18" t="n">
+        <v>-878</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="inlineStr">
@@ -2111,40 +2157,45 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
         <v>1390</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>6.51</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="7" t="n">
         <v>9630</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="7" t="n">
         <v>1070</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>2572</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>885</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>1391</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>362</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2244</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>12491</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140126</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>16.86</v>
       </c>
     </row>
@@ -2159,42 +2210,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="6" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="6" t="n">
         <v>-103</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-84</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-11</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>17</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2207,42 +2263,47 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>624</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2040</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F25" s="6" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G25" s="6" t="n">
         <v>-85</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>1902</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>-13</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-11</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-12</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-175</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2255,41 +2316,46 @@
           <t>致茂</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
         <v>1040</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>0.97</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" s="7" t="n">
         <v>1432</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="G26" s="7" t="n">
         <v>293</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>310</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-13</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>-174</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>44</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>791</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>4547</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-106283</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.15</v>
+      <c r="O26" t="n">
+        <v>3.55</v>
       </c>
     </row>
     <row r="27">
@@ -2338,6 +2404,112 @@
       </c>
       <c r="N27" t="n">
         <v>5.87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>4895</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>465</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-189</v>
+      </c>
+      <c r="I28" t="n">
+        <v>43</v>
+      </c>
+      <c r="J28" t="n">
+        <v>106</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>315</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1638</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-8879</v>
+      </c>
+      <c r="O28" t="n">
+        <v>20.94</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>27096</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>7825</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12518</v>
+      </c>
+      <c r="I29" t="n">
+        <v>380</v>
+      </c>
+      <c r="J29" t="n">
+        <v>132</v>
+      </c>
+      <c r="K29" t="n">
+        <v>362</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5847</v>
+      </c>
+      <c r="M29" t="n">
+        <v>30414</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21302</v>
+      </c>
+      <c r="O29" t="n">
+        <v>21.61</v>
       </c>
     </row>
   </sheetData>
